--- a/data/trans_bre/P2B_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 20,88</t>
+          <t>3,37; 22,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 8,75</t>
+          <t>-9,03; 9,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 13,38</t>
+          <t>-5,1; 14,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 7,21</t>
+          <t>-2,44; 7,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,44; 108,13</t>
+          <t>12,97; 116,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 16,02</t>
+          <t>-14,39; 17,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 31,68</t>
+          <t>-9,59; 35,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,2; 104,88</t>
+          <t>-18,92; 95,38</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 10,69</t>
+          <t>-0,66; 10,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 11,88</t>
+          <t>-1,95; 12,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 9,46</t>
+          <t>-1,92; 9,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 12,66</t>
+          <t>-0,36; 13,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 66,24</t>
+          <t>-3,08; 61,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 27,32</t>
+          <t>-3,57; 28,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 55,35</t>
+          <t>-8,13; 61,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 80,53</t>
+          <t>-1,6; 76,32</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,76; 20,04</t>
+          <t>5,15; 20,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 14,04</t>
+          <t>-2,23; 14,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 12,07</t>
+          <t>-2,28; 13,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 9,94</t>
+          <t>-2,24; 9,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,36; 131,98</t>
+          <t>21,76; 134,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 31,84</t>
+          <t>-4,07; 34,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 57,59</t>
+          <t>-8,84; 63,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 62,09</t>
+          <t>-10,18; 65,61</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 15,0</t>
+          <t>2,53; 15,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 12,76</t>
+          <t>-2,9; 13,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 15,28</t>
+          <t>-1,98; 14,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,22; 0,73</t>
+          <t>-21,42; -0,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,3; 134,88</t>
+          <t>14,82; 142,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 23,86</t>
+          <t>-4,68; 24,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 42,67</t>
+          <t>-4,49; 41,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-60,32; 0,94</t>
+          <t>-63,84; 0,83</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 6,93</t>
+          <t>-12,61; 6,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 12,42</t>
+          <t>-8,76; 12,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 14,58</t>
+          <t>-4,71; 16,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 2,35</t>
+          <t>-20,36; 1,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-38,24; 33,28</t>
+          <t>-39,59; 28,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 26,27</t>
+          <t>-15,05; 26,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 28,12</t>
+          <t>-7,11; 30,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-66,61; 11,83</t>
+          <t>-71,12; 8,66</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 14,0</t>
+          <t>-1,06; 12,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,81; 4,17</t>
+          <t>-13,68; 4,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 11,79</t>
+          <t>-6,62; 12,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 13,4</t>
+          <t>-1,53; 12,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 118,05</t>
+          <t>-5,59; 116,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,2; 8,48</t>
+          <t>-23,75; 9,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 31,87</t>
+          <t>-13,61; 34,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 58,68</t>
+          <t>-4,59; 53,11</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 11,04</t>
+          <t>1,18; 11,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 6,19</t>
+          <t>-5,96; 6,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 14,41</t>
+          <t>2,01; 14,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 62,31</t>
+          <t>0,24; 61,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 62,01</t>
+          <t>5,46; 68,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 14,03</t>
+          <t>-11,65; 14,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,15; 44,88</t>
+          <t>4,54; 45,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 698,86</t>
+          <t>1,43; 712,84</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 1,39</t>
+          <t>-9,26; 1,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 9,2</t>
+          <t>-2,08; 9,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 11,26</t>
+          <t>-1,09; 10,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,14; 13,7</t>
+          <t>1,71; 13,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,82; 5,05</t>
+          <t>-28,61; 5,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 18,43</t>
+          <t>-3,73; 18,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 19,67</t>
+          <t>-1,68; 18,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,81; 38,37</t>
+          <t>4,09; 37,3</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,7</t>
+          <t>1,95; 6,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 4,85</t>
+          <t>-0,45; 4,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,62; 7,92</t>
+          <t>2,47; 7,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,01; 23,77</t>
+          <t>1,97; 24,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,33; 32,93</t>
+          <t>8,87; 31,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 9,61</t>
+          <t>-0,85; 9,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,1; 19,56</t>
+          <t>5,59; 19,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,39; 103,65</t>
+          <t>8,46; 113,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2B_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,39</t>
+          <t>2,71</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,37; 22,45</t>
+          <t>3,03; 21,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 9,78</t>
+          <t>-9,47; 10,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 14,35</t>
+          <t>-4,8; 13,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 7,1</t>
+          <t>-1,94; 7,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,97; 116,05</t>
+          <t>8,39; 105,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 17,92</t>
+          <t>-15,04; 18,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 35,51</t>
+          <t>-9,89; 32,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,92; 95,38</t>
+          <t>-15,34; 97,39</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,53</t>
+          <t>6,37</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>29,16%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 10,07</t>
+          <t>-0,69; 10,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 12,16</t>
+          <t>-1,91; 12,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 9,92</t>
+          <t>-1,79; 9,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 13,1</t>
+          <t>-0,59; 12,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 61,83</t>
+          <t>-2,82; 67,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 28,45</t>
+          <t>-3,74; 28,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 61,67</t>
+          <t>-7,78; 57,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 76,32</t>
+          <t>-3,05; 68,33</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,88</t>
+          <t>2,64</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 20,11</t>
+          <t>5,31; 19,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 14,89</t>
+          <t>-2,97; 14,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 13,58</t>
+          <t>-3,29; 12,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 9,97</t>
+          <t>-3,52; 8,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,76; 134,57</t>
+          <t>22,25; 134,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 34,05</t>
+          <t>-5,64; 34,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 63,05</t>
+          <t>-11,83; 56,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 65,61</t>
+          <t>-15,43; 54,8</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-8,39</t>
+          <t>-2,25</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-30,05%</t>
+          <t>-7,88%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 15,47</t>
+          <t>3,12; 15,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 13,14</t>
+          <t>-2,9; 12,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 14,53</t>
+          <t>-1,26; 14,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,42; -0,07</t>
+          <t>-10,17; 6,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,82; 142,39</t>
+          <t>16,75; 134,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 24,57</t>
+          <t>-4,48; 24,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 41,44</t>
+          <t>-3,16; 40,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,84; 0,83</t>
+          <t>-29,46; 26,8</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-6,78</t>
+          <t>-1,79</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-29,2%</t>
+          <t>-7,39%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 6,05</t>
+          <t>-12,63; 6,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 12,34</t>
+          <t>-8,18; 13,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 16,56</t>
+          <t>-4,57; 14,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,36; 1,84</t>
+          <t>-10,21; 6,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-39,59; 28,98</t>
+          <t>-39,83; 30,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 26,02</t>
+          <t>-13,81; 29,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 30,76</t>
+          <t>-7,25; 27,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-71,12; 8,66</t>
+          <t>-33,9; 35,98</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,66</t>
+          <t>4,48</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 12,9</t>
+          <t>-1,42; 13,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 4,25</t>
+          <t>-15,05; 3,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 12,39</t>
+          <t>-8,17; 12,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 12,53</t>
+          <t>-2,48; 11,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 116,46</t>
+          <t>-8,67; 113,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,75; 9,05</t>
+          <t>-25,97; 6,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 34,02</t>
+          <t>-16,94; 32,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 53,11</t>
+          <t>-7,47; 47,5</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27,79</t>
+          <t>2,07</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>235,84%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 11,69</t>
+          <t>0,25; 11,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 6,5</t>
+          <t>-7,25; 5,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 14,66</t>
+          <t>2,4; 15,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 61,91</t>
+          <t>-2,32; 6,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,46; 68,81</t>
+          <t>1,12; 67,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 14,91</t>
+          <t>-13,94; 12,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,54; 45,49</t>
+          <t>6,19; 47,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 712,84</t>
+          <t>-16,42; 61,85</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,65</t>
+          <t>7,07</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 1,38</t>
+          <t>-9,19; 0,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 9,36</t>
+          <t>-2,42; 9,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 10,62</t>
+          <t>-0,69; 9,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,71; 13,37</t>
+          <t>1,26; 12,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,61; 5,37</t>
+          <t>-28,21; 3,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 18,68</t>
+          <t>-4,32; 19,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 18,91</t>
+          <t>-1,18; 17,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,09; 37,3</t>
+          <t>2,94; 34,54</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7,98</t>
+          <t>3,67</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,62</t>
+          <t>2,08; 6,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 4,92</t>
+          <t>-0,35; 5,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,85</t>
+          <t>2,85; 8,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,97; 24,73</t>
+          <t>1,19; 5,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,87; 31,64</t>
+          <t>8,81; 32,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 9,75</t>
+          <t>-0,67; 9,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,59; 19,51</t>
+          <t>6,59; 20,23</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,46; 113,11</t>
+          <t>4,49; 25,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2B_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Población que convive con personas que requieren dedicación o cuidados especiales</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
